--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486530_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486530_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9728</v>
+        <v>3.3016</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3285</v>
+        <v>2.5339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6444</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.1031</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1303</v>
+        <v>-0.8015</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4795</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4454</v>
+        <v>-0.3221</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7285</v>
+        <v>3.0766</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2141</v>
+        <v>1.5313</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5144</v>
+        <v>1.5452</v>
       </c>
       <c r="G3" t="n">
         <v>0.8074</v>
@@ -688,13 +688,13 @@
         <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5585</v>
+        <v>-1.2104</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.6741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5671</v>
+        <v>-0.5363</v>
       </c>
       <c r="V3" t="n">
         <v>1.3045</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1222</v>
+        <v>2.7361</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3457</v>
+        <v>2.7747</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2235</v>
+        <v>-0.0386</v>
       </c>
       <c r="G4" t="n">
         <v>3.7643</v>
@@ -766,13 +766,13 @@
         <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2947</v>
+        <v>-0.6808</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2774</v>
+        <v>-0.8484</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0173</v>
+        <v>0.1676</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5649999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.14</v>
+        <v>1.7471</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4609</v>
+        <v>2.8214</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.321</v>
+        <v>-1.0744</v>
       </c>
       <c r="G5" t="n">
         <v>1.1076</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6201</v>
+        <v>-1.013</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0719</v>
+        <v>-0.7114</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5482</v>
+        <v>-0.3016</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.059</v>
+        <v>1.2029</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8189</v>
+        <v>2.0244</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7599</v>
+        <v>-0.8215</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6019</v>
@@ -922,13 +922,13 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9916</v>
+        <v>-0.8478</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6609</v>
+        <v>-0.4554</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3307</v>
+        <v>-0.3924</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0468</v>
+        <v>0.3641</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6765</v>
+        <v>0.584</v>
       </c>
       <c r="G7" t="n">
         <v>2.4</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3717</v>
+        <v>-0.1469</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>-0.2307</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1763</v>
+        <v>0.0838</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4328</v>
+        <v>-1.1555</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9971</v>
+        <v>0.667</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4357</v>
+        <v>-1.8224</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0775</v>
+        <v>-0.657</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4683</v>
+        <v>0.1216</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5458</v>
+        <v>-0.7786</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2154</v>
+        <v>1.7321</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4348</v>
+        <v>0.2404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6502</v>
+        <v>1.4917</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1379</v>
+        <v>-2.3891</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0335</v>
+        <v>-0.1188</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1044</v>
+        <v>-2.2703</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5104</v>
+        <v>-0.2385</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.125</v>
+        <v>-0.3256</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3854</v>
+        <v>0.0871</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4428</v>
+        <v>-1.2286</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1947</v>
+        <v>-0.8853</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6375</v>
+        <v>-0.3433</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.657</v>
+        <v>0.0775</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1216</v>
+        <v>-0.4683</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7786</v>
+        <v>0.5458</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7321</v>
+        <v>0.2154</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2404</v>
+        <v>-0.4348</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4917</v>
+        <v>0.6502</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3891</v>
+        <v>-0.1379</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1188</v>
+        <v>-0.0335</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2703</v>
+        <v>-0.1044</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5259</v>
+        <v>-0.3061</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.0132</v>
       </c>
       <c r="U9" t="n">
-        <v>0.272</v>
+        <v>-0.2929</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7174</v>
+        <v>-1.7887</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3851</v>
+        <v>0.874</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3323</v>
+        <v>-2.6628</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1702</v>
+        <v>3.7127</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4562</v>
+        <v>2.5732</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6264</v>
+        <v>1.1395</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5756</v>
+        <v>4.4068</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6086</v>
+        <v>1.9955</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1841</v>
+        <v>2.4113</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5946</v>
+        <v>-0.6942</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1523</v>
+        <v>0.5776</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4423</v>
+        <v>-1.2718</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>1.735</v>
+        <v>-0.7189</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0827</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6523</v>
+        <v>0.1163</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0647</v>
+        <v>-2.8249</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2599</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1916</v>
+        <v>-2.5791</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6253</v>
+        <v>-3.5455</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8169</v>
+        <v>0.9665</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7127</v>
+        <v>-2.4835</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5732</v>
+        <v>-1.332</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1395</v>
+        <v>-1.1515</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4068</v>
+        <v>-1.6913</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9955</v>
+        <v>-1.5782</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4113</v>
+        <v>-0.1131</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6942</v>
+        <v>-0.7922</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5776</v>
+        <v>0.2461</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2718</v>
+        <v>-1.0383</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1218</v>
+        <v>-0.7481</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0839</v>
+        <v>-0.7667</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0379</v>
+        <v>0.0186</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.8249</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3963</v>
+        <v>-2.9831</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7943</v>
+        <v>-1.5892</v>
       </c>
       <c r="F12" t="n">
-        <v>1.398</v>
+        <v>-1.3939</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4835</v>
+        <v>-1.1702</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.332</v>
+        <v>0.4562</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1515</v>
+        <v>-1.6264</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6913</v>
+        <v>-0.5756</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5782</v>
+        <v>0.6086</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1131</v>
+        <v>-1.1841</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7922</v>
+        <v>-0.5946</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2461</v>
+        <v>-0.1523</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0383</v>
+        <v>-0.4423</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5653</v>
+        <v>0.4693</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0154</v>
+        <v>-0.1214</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4501</v>
+        <v>0.5906</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.0647</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.564899999999999</v>
+        <v>3.277399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8584</v>
+        <v>7.570800000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2935</v>
+        <v>-4.2936</v>
       </c>
       <c r="G13" t="n">
         <v>7.06</v>
@@ -1468,13 +1468,13 @@
         <v>17.4005</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.955299999999998</v>
+        <v>-6.242699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.174100000000001</v>
+        <v>-5.461600000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7813000000000003</v>
+        <v>-0.7813000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8902</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.389</v>
+        <v>4.9311</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1885</v>
+        <v>2.7356</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2006</v>
+        <v>2.1954</v>
       </c>
       <c r="G14" t="n">
         <v>-0.1081</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5624</v>
+        <v>2.1045</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3878</v>
+        <v>0.9349</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1746</v>
+        <v>1.1695</v>
       </c>
       <c r="V14" t="n">
         <v>2.0647</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4964</v>
+        <v>4.6749</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9407</v>
+        <v>4.6054</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4443</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0.9177999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4285</v>
+        <v>1.607</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6922</v>
+        <v>0.3569</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7363</v>
+        <v>1.2501</v>
       </c>
       <c r="V15" t="n">
         <v>3.0202</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9003</v>
+        <v>3.7121</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9737</v>
+        <v>3.4208</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.2913</v>
       </c>
       <c r="G16" t="n">
         <v>2.0153</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6577</v>
+        <v>0.1541</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0273</v>
+        <v>0.392</v>
       </c>
       <c r="V16" t="n">
         <v>1.3252</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.854</v>
+        <v>1.2412</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2288</v>
+        <v>2.0739</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6252</v>
+        <v>-0.8327</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3981</v>
+        <v>2.5212</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8196</v>
+        <v>-1.6759</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.2177</v>
+        <v>4.1971</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3057</v>
+        <v>4.5597</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5065</v>
+        <v>-0.7601</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2008</v>
+        <v>5.3199</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7038</v>
+        <v>-2.0386</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3131</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0169</v>
+        <v>-1.1228</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R17" t="n">
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0346</v>
+        <v>1.0049</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0106</v>
+        <v>-0.2211</v>
       </c>
       <c r="U17" t="n">
-        <v>1.024</v>
+        <v>1.226</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1917</v>
+        <v>1.0551</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2916</v>
+        <v>0.5582</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0999</v>
+        <v>0.4968</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5212</v>
+        <v>-0.3981</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6759</v>
+        <v>2.8196</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1971</v>
+        <v>-3.2177</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5597</v>
+        <v>1.3057</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7601</v>
+        <v>2.5065</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3199</v>
+        <v>-1.2008</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0386</v>
+        <v>-1.7038</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9157999999999999</v>
+        <v>0.3131</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1228</v>
+        <v>-2.0169</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.0451</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0446</v>
+        <v>1.2356</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0034</v>
+        <v>0.3401</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9588</v>
+        <v>0.8956</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6167</v>
+        <v>-0.3868</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0907</v>
+        <v>0.021</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.526</v>
+        <v>-0.4078</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6526999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1816</v>
+        <v>0.0484</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0239</v>
+        <v>0.1421</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8213</v>
+        <v>-1.4184</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5164</v>
+        <v>-1.519</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3049</v>
+        <v>0.1007</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3196</v>
+        <v>-2.6065</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7427</v>
+        <v>0.5259</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4231</v>
+        <v>-3.1325</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5986</v>
+        <v>-0.4844</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7784</v>
+        <v>0.1642</v>
       </c>
       <c r="L20" t="n">
-        <v>1.377</v>
+        <v>-0.6486</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9182</v>
+        <v>-2.1222</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9643</v>
+        <v>0.3617</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9539</v>
+        <v>-2.4838</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9334</v>
+        <v>0.9707</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0601</v>
+        <v>0.0529</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8733</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3878</v>
+        <v>-1.8765</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.764</v>
+        <v>-1.6281</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6238</v>
+        <v>-0.2484</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3555</v>
+        <v>-1.3196</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2934</v>
+        <v>-1.7427</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9379</v>
+        <v>0.4231</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8082</v>
+        <v>0.5986</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1963</v>
+        <v>-0.7784</v>
       </c>
       <c r="L21" t="n">
-        <v>0.612</v>
+        <v>1.377</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4528</v>
+        <v>-1.9182</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.9643</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5499</v>
+        <v>-0.9539</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.8276</v>
+        <v>-0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>0.584</v>
+        <v>0.8781</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0601</v>
+        <v>-0.0517</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5239</v>
+        <v>0.9298</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4997</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5295</v>
+        <v>-2.4623</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3013</v>
+        <v>-0.9875</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2282</v>
+        <v>-1.4748</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6065</v>
+        <v>1.3555</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5259</v>
+        <v>2.2934</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1325</v>
+        <v>-0.9379</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4844</v>
+        <v>2.8082</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1642</v>
+        <v>2.1963</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6486</v>
+        <v>0.612</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1222</v>
+        <v>-1.4528</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3617</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4838</v>
+        <v>-1.5499</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2175</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1405</v>
+        <v>0.5095</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7294</v>
+        <v>-0.1634</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5889</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.4997</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0942</v>
+        <v>-3.3068</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2366</v>
+        <v>-3.9013</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1424</v>
+        <v>0.5945</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5788</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1027</v>
+        <v>0.6847</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6249</v>
+        <v>-0.2896</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5221</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>0.9347</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9466</v>
+        <v>-5.4932</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4206</v>
+        <v>-1.0854</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.526</v>
+        <v>-4.4078</v>
       </c>
       <c r="G24" t="n">
         <v>-3.206</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5394</v>
+        <v>0.9929</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1815</v>
+        <v>0.1538</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7209</v>
+        <v>0.8391</v>
       </c>
       <c r="V24" t="n">
         <v>-4.1501</v>
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.564699999999999</v>
+        <v>0.6704000000000017</v>
       </c>
       <c r="E25" t="n">
-        <v>4.293700000000002</v>
+        <v>4.293599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.8583</v>
+        <v>-3.6233</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.06</v>
+        <v>-7.059999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>2.4027</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.4627</v>
+        <v>-9.462700000000002</v>
       </c>
       <c r="J25" t="n">
         <v>12.3965</v>
       </c>
       <c r="K25" t="n">
-        <v>5.415999999999999</v>
+        <v>5.416</v>
       </c>
       <c r="L25" t="n">
-        <v>6.9809</v>
+        <v>6.980900000000002</v>
       </c>
       <c r="M25" t="n">
         <v>-19.4569</v>
@@ -2404,19 +2404,19 @@
         <v>13.0502</v>
       </c>
       <c r="S25" t="n">
-        <v>7.9552</v>
+        <v>10.1904</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7810999999999995</v>
+        <v>0.7811999999999997</v>
       </c>
       <c r="U25" t="n">
-        <v>7.174</v>
+        <v>9.4092</v>
       </c>
       <c r="V25" t="n">
         <v>1.8902</v>
       </c>
       <c r="W25" t="n">
-        <v>8.516199999999998</v>
+        <v>8.5162</v>
       </c>
       <c r="X25" t="n">
         <v>-6.625999999999999</v>
